--- a/01_Mechanic/02_Manufacturing/01_CNC/CMF说明/RP1_CNC_CMF_Specification.xlsx
+++ b/01_Mechanic/02_Manufacturing/01_CNC/CMF说明/RP1_CNC_CMF_Specification.xlsx
@@ -151,7 +151,7 @@
     <t>YCL.M000331</t>
   </si>
   <si>
-    <t>雷赛灵巧手转接件</t>
+    <t>灵巧手转接件</t>
   </si>
   <si>
     <t>YCL.M000342</t>

--- a/01_Mechanic/02_Manufacturing/01_CNC/CMF说明/RP1_CNC_CMF_Specification.xlsx
+++ b/01_Mechanic/02_Manufacturing/01_CNC/CMF说明/RP1_CNC_CMF_Specification.xlsx
@@ -151,7 +151,7 @@
     <t>YCL.M000331</t>
   </si>
   <si>
-    <t>灵巧手转接件</t>
+    <t>RP_Hand转接件</t>
   </si>
   <si>
     <t>YCL.M000342</t>
